--- a/sample_data/example4_mixed/period2_may_2025.xlsx
+++ b/sample_data/example4_mixed/period2_may_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,57 +446,92 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>region</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>account_manager</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>industry</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>support_tier</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>employee_count</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>contract_value_usd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>renewal_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rate_pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>contract_value_usd</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>nps_score</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>last_contact_date</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>open_support_tickets</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>product_modules_used</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>logins_last_30_days</t>
         </is>
       </c>
     </row>
@@ -508,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACC-001</t>
+          <t>ACC-0001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,48 +553,75 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Dana Lee</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5200</v>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12150</v>
+      </c>
+      <c r="K2" t="n">
+        <v>386530</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5480</v>
-      </c>
-      <c r="K2" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>80</v>
-      </c>
-      <c r="M2" t="n">
-        <v>124000</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
+      <c r="N2" t="n">
+        <v>7453</v>
+      </c>
+      <c r="O2" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P2" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>57</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +632,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACC-002</t>
+          <t>ACC-0002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -580,21 +642,23 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tom Walsh</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Logistics</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1800</v>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,25 +667,50 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2800</v>
+        <v>19916</v>
       </c>
       <c r="K3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="L3" t="n">
-        <v>71</v>
-      </c>
-      <c r="M3" t="n">
-        <v>48000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-05-15</t>
-        </is>
+        <v>414131</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3052</v>
+      </c>
+      <c r="O3" t="n">
+        <v>79</v>
+      </c>
+      <c r="P3" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -632,7 +721,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACC-003</t>
+          <t>ACC-0003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,48 +731,75 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Dana Lee</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3400</v>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Mid-Market</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2803</v>
+      </c>
+      <c r="K4" t="n">
+        <v>69462</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5100</v>
-      </c>
-      <c r="K4" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>85</v>
-      </c>
-      <c r="M4" t="n">
-        <v>98000</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-05-29</t>
-        </is>
+      <c r="N4" t="n">
+        <v>4015</v>
+      </c>
+      <c r="O4" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -694,7 +810,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACC-004</t>
+          <t>ACC-0004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -704,48 +820,75 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>APAC</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Priya Nair</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>8900</v>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SMB</t>
+          <t>Mid-Market</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2381</v>
+      </c>
+      <c r="K5" t="n">
+        <v>149184</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>7450</v>
-      </c>
-      <c r="K5" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L5" t="n">
-        <v>69</v>
-      </c>
-      <c r="M5" t="n">
-        <v>210000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
+      <c r="N5" t="n">
+        <v>8566</v>
+      </c>
+      <c r="O5" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +899,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACC-005</t>
+          <t>ACC-0005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,21 +909,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Tom Walsh</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>620</v>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -789,25 +934,50 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1200</v>
+        <v>1916</v>
       </c>
       <c r="K6" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>22000</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-05-10</t>
-        </is>
+        <v>135102</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1582</v>
+      </c>
+      <c r="O6" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -818,7 +988,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACC-006</t>
+          <t>ACC-0006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -828,48 +998,75 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>EMEA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Carlos Rivera</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2100</v>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>8266</v>
+      </c>
+      <c r="K7" t="n">
+        <v>370407</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="K7" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>82</v>
-      </c>
-      <c r="M7" t="n">
-        <v>75000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-05-27</t>
-        </is>
+      <c r="N7" t="n">
+        <v>5072</v>
+      </c>
+      <c r="O7" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>28</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +1077,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACC-007</t>
+          <t>ACC-0007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -890,48 +1087,75 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Dana Lee</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>450</v>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SMB</t>
+          <t>Mid-Market</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>820</v>
+        <v>2571</v>
       </c>
       <c r="K8" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>64</v>
-      </c>
-      <c r="M8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-05-08</t>
-        </is>
+        <v>131270</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1269</v>
+      </c>
+      <c r="O8" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>98</v>
       </c>
     </row>
     <row r="9">
@@ -942,7 +1166,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACC-008</t>
+          <t>ACC-0008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -952,48 +1176,75 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Emma Thompson</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1200</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mid-Market</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>14262</v>
+      </c>
+      <c r="K9" t="n">
+        <v>301167</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>3800</v>
-      </c>
-      <c r="K9" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>74</v>
-      </c>
-      <c r="M9" t="n">
-        <v>52000</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-05-25</t>
-        </is>
+      <c r="N9" t="n">
+        <v>3434</v>
+      </c>
+      <c r="O9" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>26</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -1004,7 +1255,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACC-009</t>
+          <t>ACC-0009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1014,48 +1265,75 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tom Walsh</t>
+          <t>APAC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>4100</v>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Mid-Market</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>24882</v>
+      </c>
+      <c r="K10" t="n">
+        <v>420695</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>4350</v>
-      </c>
-      <c r="K10" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>83</v>
-      </c>
-      <c r="M10" t="n">
-        <v>115000</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
+      <c r="N10" t="n">
+        <v>8499</v>
+      </c>
+      <c r="O10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>18</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -1066,7 +1344,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ACC-010</t>
+          <t>ACC-0010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,48 +1354,75 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Carlos Rivera</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Airlines</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>12000</v>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mid-Market</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>17636</v>
+      </c>
+      <c r="K11" t="n">
+        <v>410185</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>8400</v>
-      </c>
-      <c r="K11" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>68</v>
-      </c>
-      <c r="M11" t="n">
-        <v>380000</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
+      <c r="N11" t="n">
+        <v>5720</v>
+      </c>
+      <c r="O11" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>62</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -1128,7 +1433,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACC-011</t>
+          <t>ACC-0011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1138,48 +1443,75 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>APAC</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Priya Nair</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>6700</v>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>23182</v>
+      </c>
+      <c r="K12" t="n">
+        <v>397105</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>6600</v>
-      </c>
-      <c r="K12" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="L12" t="n">
-        <v>79</v>
-      </c>
-      <c r="M12" t="n">
-        <v>175000</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-05-26</t>
-        </is>
+      <c r="N12" t="n">
+        <v>3038</v>
+      </c>
+      <c r="O12" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>27</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1190,7 +1522,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACC-012</t>
+          <t>ACC-0012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1200,48 +1532,6127 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3757</v>
+      </c>
+      <c r="K13" t="n">
+        <v>241955</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>6406</v>
+      </c>
+      <c r="O13" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>49</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ACC-0013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marble Dynamics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>17528</v>
+      </c>
+      <c r="K14" t="n">
+        <v>276154</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2378</v>
+      </c>
+      <c r="O14" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>14</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ACC-0014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nova Legal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>18227</v>
+      </c>
+      <c r="K15" t="n">
+        <v>328640</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1264</v>
+      </c>
+      <c r="O15" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>45</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ACC-0015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Orbit Digital</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>11216</v>
+      </c>
+      <c r="K16" t="n">
+        <v>149276</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5600</v>
+      </c>
+      <c r="O16" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ACC-0016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pinnacle Ventures</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>18653</v>
+      </c>
+      <c r="K17" t="n">
+        <v>229491</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5464</v>
+      </c>
+      <c r="O17" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>39</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ACC-0017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quorum Analytics</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Dana Lee</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2172</v>
+      </c>
+      <c r="K18" t="n">
+        <v>214901</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1832</v>
+      </c>
+      <c r="O18" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>31</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ACC-0018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Redwood Biotech</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>15407</v>
+      </c>
+      <c r="K19" t="n">
+        <v>361864</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1227</v>
+      </c>
+      <c r="O19" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>23</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ACC-0019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Summit Architecture</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>20531</v>
+      </c>
+      <c r="K20" t="n">
+        <v>260446</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>6398</v>
+      </c>
+      <c r="O20" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>40</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ACC-0020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tidal Payments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>9859</v>
+      </c>
+      <c r="K21" t="n">
+        <v>204862</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>4720</v>
+      </c>
+      <c r="O21" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="P21" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>57</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACC-0021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Umbrella Security</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4776</v>
+      </c>
+      <c r="K22" t="n">
+        <v>246718</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>8590</v>
+      </c>
+      <c r="O22" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>16</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ACC-0022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vertex Robotics</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>304</v>
+      </c>
+      <c r="K23" t="n">
+        <v>84085</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>3683</v>
+      </c>
+      <c r="O23" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>55</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>11</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACC-0023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Wavelength Audio</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>6857</v>
+      </c>
+      <c r="K24" t="n">
+        <v>121123</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>3415</v>
+      </c>
+      <c r="O24" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>56</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ACC-0024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Xenon Aerospace</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>20539</v>
+      </c>
+      <c r="K25" t="n">
+        <v>361885</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>4767</v>
+      </c>
+      <c r="O25" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>27</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ACC-0025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yellowstone Mining</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>21027</v>
+      </c>
+      <c r="K26" t="n">
+        <v>65675</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>8239</v>
+      </c>
+      <c r="O26" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>49</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>16</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ACC-0026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zephyr Mobility</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>15441</v>
+      </c>
+      <c r="K27" t="n">
+        <v>309730</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>7102</v>
+      </c>
+      <c r="O27" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="P27" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>28</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>16</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ACC-0027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Anchor Fintech</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>6470</v>
+      </c>
+      <c r="K28" t="n">
+        <v>409175</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>6839</v>
+      </c>
+      <c r="O28" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>46</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ACC-0028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Beacon Publishing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>6535</v>
+      </c>
+      <c r="K29" t="n">
+        <v>310162</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>8143</v>
+      </c>
+      <c r="O29" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>46</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ACC-0029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Cascade Networks</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>21122</v>
+      </c>
+      <c r="K30" t="n">
+        <v>291254</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>7194</v>
+      </c>
+      <c r="O30" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>54</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ACC-0030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Driftwood Creative</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>14611</v>
+      </c>
+      <c r="K31" t="n">
+        <v>325092</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>4520</v>
+      </c>
+      <c r="O31" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>45</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ACC-0031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Eclipse Automotive</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>19659</v>
+      </c>
+      <c r="K32" t="n">
+        <v>72130</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>2745</v>
+      </c>
+      <c r="O32" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>32</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ACC-0032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Forge Industries</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>9290</v>
+      </c>
+      <c r="K33" t="n">
+        <v>68552</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>1663</v>
+      </c>
+      <c r="O33" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>59</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ACC-0033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Glacier Properties</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>20940</v>
+      </c>
+      <c r="K34" t="n">
+        <v>445510</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>3877</v>
+      </c>
+      <c r="O34" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>38</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ACC-0034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Halo Sportswear</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>11795</v>
+      </c>
+      <c r="K35" t="n">
+        <v>196633</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>6956</v>
+      </c>
+      <c r="O35" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P35" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>16</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ACC-0035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Indigo Hospitality</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>16873</v>
+      </c>
+      <c r="K36" t="n">
+        <v>189784</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>3315</v>
+      </c>
+      <c r="O36" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>41</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ACC-0036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jade Commerce</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>21288</v>
+      </c>
+      <c r="K37" t="n">
+        <v>78003</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>2894</v>
+      </c>
+      <c r="O37" t="n">
+        <v>85</v>
+      </c>
+      <c r="P37" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>52</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ACC-0037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kite Insurance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>8835</v>
+      </c>
+      <c r="K38" t="n">
+        <v>331972</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>4977</v>
+      </c>
+      <c r="O38" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="P38" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>10</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ACC-0038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lattice Software</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>19707</v>
+      </c>
+      <c r="K39" t="n">
+        <v>23037</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>4745</v>
+      </c>
+      <c r="O39" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="P39" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>43</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ACC-0039</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mosaic Events</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>16346</v>
+      </c>
+      <c r="K40" t="n">
+        <v>86107</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>6570</v>
+      </c>
+      <c r="O40" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="P40" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>12</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>14</v>
+      </c>
+      <c r="T40" t="n">
+        <v>7</v>
+      </c>
+      <c r="U40" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ACC-0040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nectar Foods</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>12456</v>
+      </c>
+      <c r="K41" t="n">
+        <v>107232</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4202</v>
+      </c>
+      <c r="O41" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>34</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
+        <v>17</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ACC-0041</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Onyx Engineering</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>20736</v>
+      </c>
+      <c r="K42" t="n">
+        <v>420282</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>3557</v>
+      </c>
+      <c r="O42" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="P42" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>31</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>16</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ACC-0042</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prism Textiles</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>11024</v>
+      </c>
+      <c r="K43" t="n">
+        <v>427943</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4698</v>
+      </c>
+      <c r="O43" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>53</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>17</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ACC-0043</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Quest Shipping</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>18748</v>
+      </c>
+      <c r="K44" t="n">
+        <v>43009</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2243</v>
+      </c>
+      <c r="O44" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="P44" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ACC-0044</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ridge Agriculture</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K45" t="n">
+        <v>69640</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>5669</v>
+      </c>
+      <c r="O45" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>11</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ACC-0045</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sterling Media</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>21557</v>
+      </c>
+      <c r="K46" t="n">
+        <v>430473</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5765</v>
+      </c>
+      <c r="O46" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>49</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ACC-0046</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tempest Clean Energy</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>24115</v>
+      </c>
+      <c r="K47" t="n">
+        <v>288380</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>5939</v>
+      </c>
+      <c r="O47" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>39</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>17</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ACC-0047</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Union Telecom</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>24589</v>
+      </c>
+      <c r="K48" t="n">
+        <v>329388</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>3348</v>
+      </c>
+      <c r="O48" t="n">
+        <v>64</v>
+      </c>
+      <c r="P48" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>27</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>7</v>
+      </c>
+      <c r="U48" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ACC-0048</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Vantage Wealth</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>21113</v>
+      </c>
+      <c r="K49" t="n">
+        <v>258869</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>8853</v>
+      </c>
+      <c r="O49" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="P49" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>60</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ACC-0049</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wildfire Gaming</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>17269</v>
+      </c>
+      <c r="K50" t="n">
+        <v>108442</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>6381</v>
+      </c>
+      <c r="O50" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>18</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ACC-0050</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Xcel Healthcare</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>18542</v>
+      </c>
+      <c r="K51" t="n">
+        <v>330825</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>7909</v>
+      </c>
+      <c r="O51" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="P51" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>18</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ACC-0051</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Yarrow Cosmetics</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>23206</v>
+      </c>
+      <c r="K52" t="n">
+        <v>87960</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>8074</v>
+      </c>
+      <c r="O52" t="n">
+        <v>60</v>
+      </c>
+      <c r="P52" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>36</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ACC-0052</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Zenith Aerospace</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>18267</v>
+      </c>
+      <c r="K53" t="n">
+        <v>20879</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4587</v>
+      </c>
+      <c r="O53" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="P53" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>20</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>16</v>
+      </c>
+      <c r="T53" t="n">
+        <v>7</v>
+      </c>
+      <c r="U53" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ACC-0053</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Alpine Consulting</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>6830</v>
+      </c>
+      <c r="K54" t="n">
+        <v>377998</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>4327</v>
+      </c>
+      <c r="O54" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ACC-0054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bright Futures NGO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>4032</v>
+      </c>
+      <c r="K55" t="n">
+        <v>175901</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1908</v>
+      </c>
+      <c r="O55" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="P55" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>55</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ACC-0055</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cobalt Semiconductors</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>24338</v>
+      </c>
+      <c r="K56" t="n">
+        <v>25646</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>7746</v>
+      </c>
+      <c r="O56" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="P56" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>58</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>2</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ACC-0056</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Dawn Hospitality</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>3521</v>
+      </c>
+      <c r="K57" t="n">
+        <v>200011</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="P57" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>56</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ACC-0057</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ember Logistics</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>22762</v>
+      </c>
+      <c r="K58" t="n">
+        <v>58511</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>4230</v>
+      </c>
+      <c r="O58" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="P58" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>50</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="n">
+        <v>7</v>
+      </c>
+      <c r="U58" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ACC-0058</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Flux Analytics</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>23401</v>
+      </c>
+      <c r="K59" t="n">
+        <v>216172</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1870</v>
+      </c>
+      <c r="O59" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="P59" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>24</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="n">
+        <v>6</v>
+      </c>
+      <c r="U59" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ACC-0059</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Grove Pharma</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1079</v>
+      </c>
+      <c r="K60" t="n">
+        <v>305402</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>6346</v>
+      </c>
+      <c r="O60" t="n">
+        <v>57</v>
+      </c>
+      <c r="P60" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>38</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
+        <v>12</v>
+      </c>
+      <c r="T60" t="n">
+        <v>7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ACC-0060</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Haven Insurance</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>20191</v>
+      </c>
+      <c r="K61" t="n">
+        <v>157451</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2683</v>
+      </c>
+      <c r="O61" t="n">
+        <v>61</v>
+      </c>
+      <c r="P61" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>21</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ACC-0061</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Impact Ventures</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>310</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>14781</v>
+      </c>
+      <c r="K62" t="n">
+        <v>42196</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>8512</v>
+      </c>
+      <c r="O62" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="P62" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>56</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ACC-0062</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Junction Rail</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>9769</v>
+      </c>
+      <c r="K63" t="n">
+        <v>401506</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1443</v>
+      </c>
+      <c r="O63" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P63" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>14</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>12</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ACC-0063</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Knoll Architecture</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>12599</v>
+      </c>
+      <c r="K64" t="n">
+        <v>247230</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>8739</v>
+      </c>
+      <c r="O64" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="P64" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>61</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ACC-0064</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Lark Media</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>10741</v>
+      </c>
+      <c r="K65" t="n">
+        <v>18215</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5012</v>
+      </c>
+      <c r="O65" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="P65" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
+        <v>14</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ACC-0065</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Mantis Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>20399</v>
+      </c>
+      <c r="K66" t="n">
+        <v>261731</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>8979</v>
+      </c>
+      <c r="O66" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="P66" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ACC-0066</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nimbus Cloud</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>10319</v>
+      </c>
+      <c r="K67" t="n">
+        <v>416306</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>3182</v>
+      </c>
+      <c r="O67" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="P67" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>73</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ACC-0067</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Obsidian Mining</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>3202</v>
+      </c>
+      <c r="K68" t="n">
+        <v>15899</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>7226</v>
+      </c>
+      <c r="O68" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="P68" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>29</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
+        <v>16</v>
+      </c>
+      <c r="T68" t="n">
+        <v>8</v>
+      </c>
+      <c r="U68" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ACC-0068</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Pulse Wearables</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>9951</v>
+      </c>
+      <c r="K69" t="n">
+        <v>355720</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>456</v>
+      </c>
+      <c r="O69" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="P69" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>43</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
+        <v>3</v>
+      </c>
+      <c r="T69" t="n">
+        <v>7</v>
+      </c>
+      <c r="U69" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ACC-0069</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Quartz Construction</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>13214</v>
+      </c>
+      <c r="K70" t="n">
+        <v>174706</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>4841</v>
+      </c>
+      <c r="O70" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="P70" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>27</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
+        <v>11</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ACC-0070</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Raven Defense</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>11286</v>
+      </c>
+      <c r="K71" t="n">
+        <v>320744</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>2752</v>
+      </c>
+      <c r="O71" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="P71" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>36</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
+        <v>12</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ACC-0071</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Solace Health</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>12556</v>
+      </c>
+      <c r="K72" t="n">
+        <v>20610</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>6376</v>
+      </c>
+      <c r="O72" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>75</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ACC-0072</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Thorn Agritech</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>24677</v>
+      </c>
+      <c r="K73" t="n">
+        <v>408869</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>7931</v>
+      </c>
+      <c r="O73" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="P73" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>43</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>5</v>
+      </c>
+      <c r="U73" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ACC-0073</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Uplift Finance</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>9918</v>
+      </c>
+      <c r="K74" t="n">
+        <v>435363</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4622</v>
+      </c>
+      <c r="O74" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="P74" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>42</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+      <c r="T74" t="n">
+        <v>7</v>
+      </c>
+      <c r="U74" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ACC-0074</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Valor Logistics</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>20458</v>
+      </c>
+      <c r="K75" t="n">
+        <v>251052</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>3276</v>
+      </c>
+      <c r="O75" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>68</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="n">
+        <v>5</v>
+      </c>
+      <c r="U75" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ACC-0075</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wren Publishing</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dana Lee</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>SMB</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>24804</v>
+      </c>
+      <c r="K76" t="n">
+        <v>103172</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>6675</v>
+      </c>
+      <c r="O76" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="P76" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>23</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ACC-0076</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Axis Motors</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>20772</v>
+      </c>
+      <c r="K77" t="n">
+        <v>74829</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>9000</v>
+      </c>
+      <c r="O77" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="P77" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>37</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ACC-0077</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bloom Biotech</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tom Walsh</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>13511</v>
+      </c>
+      <c r="K78" t="n">
+        <v>312851</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>4420</v>
+      </c>
+      <c r="O78" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="P78" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>29</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="n">
+        <v>8</v>
+      </c>
+      <c r="U78" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ACC-0078</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cipher Networks</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>24736</v>
+      </c>
+      <c r="K79" t="n">
+        <v>358719</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>600</v>
-      </c>
-      <c r="K13" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>61</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-05-05</t>
-        </is>
+      <c r="N79" t="n">
+        <v>7272</v>
+      </c>
+      <c r="O79" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="P79" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>51</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
+        <v>11</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ACC-0079</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dusk Realty</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Mid-Market</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>10360</v>
+      </c>
+      <c r="K80" t="n">
+        <v>305804</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>4658</v>
+      </c>
+      <c r="O80" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>47</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>8</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ACC-0080</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Eagle Fintech</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Emma Thompson</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SMB</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>7020</v>
+      </c>
+      <c r="K81" t="n">
+        <v>226069</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>8918</v>
+      </c>
+      <c r="O81" t="n">
+        <v>78</v>
+      </c>
+      <c r="P81" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>43</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="n">
+        <v>5</v>
+      </c>
+      <c r="U81" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
